--- a/report/downloads/reports/网点变化对比报告_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
     </row>
@@ -11368,22 +11368,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11393,29 +11393,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11425,29 +11425,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11457,29 +11457,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11489,29 +11489,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11521,29 +11521,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11553,29 +11553,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11602,12 +11602,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11617,29 +11617,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11661,17 +11661,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11681,29 +11681,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11713,29 +11713,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11757,17 +11757,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11777,29 +11777,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11809,29 +11809,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11853,17 +11853,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
@@ -11885,17 +11885,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11905,29 +11905,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11937,29 +11937,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11981,17 +11981,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -12013,17 +12013,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12033,29 +12033,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
@@ -12109,17 +12109,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -12141,17 +12141,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -12173,17 +12173,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12193,29 +12193,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12225,29 +12225,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12257,29 +12257,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -12328,22 +12328,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12424,22 +12424,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12456,22 +12456,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12493,17 +12493,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12552,22 +12552,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
     </row>
@@ -11368,22 +11368,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11393,29 +11393,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11425,29 +11425,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11457,29 +11457,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
@@ -11501,17 +11501,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11521,29 +11521,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11565,17 +11565,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11585,29 +11585,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
@@ -11629,17 +11629,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11666,12 +11666,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11681,29 +11681,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11713,29 +11713,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11745,29 +11745,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11777,29 +11777,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11821,17 +11821,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11841,29 +11841,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11873,29 +11873,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
@@ -11917,17 +11917,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11937,29 +11937,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11981,17 +11981,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12001,14 +12001,14 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -12045,17 +12045,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12065,29 +12065,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -12114,12 +12114,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12129,29 +12129,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12161,29 +12161,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12193,14 +12193,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12225,29 +12225,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
@@ -12269,17 +12269,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12360,22 +12360,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12424,22 +12424,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12456,22 +12456,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12488,22 +12488,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12552,22 +12552,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
